--- a/data/trans_dic/IP31C_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 19,87</t>
+          <t>5,66; 24,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 22,4</t>
+          <t>5,71; 24,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 18,16</t>
+          <t>7,35; 20,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,91</t>
+          <t>6,16; 10,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,94</t>
+          <t>5,84; 11,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,76</t>
+          <t>6,68; 10,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 17,52</t>
+          <t>11,87; 21,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 19,77</t>
+          <t>9,16; 18,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 16,25</t>
+          <t>11,65; 18,76</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,42</t>
+          <t>8,8; 13,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,84</t>
+          <t>7,46; 11,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,64</t>
+          <t>8,73; 11,97</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12692</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2428; 10670</t>
+          <t>3039; 12909</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3122; 13067</t>
+          <t>2622; 11222</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7731; 20352</t>
+          <t>7320; 20497</t>
         </is>
       </c>
     </row>
@@ -906,17 +906,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>39791</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>33864</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>73654</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17252; 35583</t>
+          <t>28606; 50809</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24846; 44979</t>
+          <t>24723; 47761</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45172; 73987</t>
+          <t>59319; 91207</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>46498</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11433; 25546</t>
+          <t>19779; 36656</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17873; 35810</t>
+          <t>13443; 27470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31445; 53129</t>
+          <t>36519; 58813</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35780; 61210</t>
+          <t>60289; 90234</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52179; 80544</t>
+          <t>45924; 73682</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94565; 134264</t>
+          <t>113590; 155748</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31C_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que realizan algún voluntariado (tasa de respuesta: 99,62%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,66; 24,03</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,71; 24,45</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,35; 20,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 10,93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,84; 11,29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,68; 10,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11,87; 21,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,16; 18,71</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>11,65; 18,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>8,8; 13,17</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,46; 11,96</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,73; 11,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1252005620528129</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1299932804262557</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.127409052136942</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5967</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12692</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.05657341200568895</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.05711597990212833</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.07347692002725952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3039; 12909</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2622; 11222</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7320; 20497</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2403208366602436</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2444516994084052</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2057541428054018</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.08563228008183352</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.08003388767857815</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.08296411056156183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33864</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73654</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.06156165882243991</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.05843121452391713</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.0668167204972408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>28606; 50809</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>24723; 47761</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>59319; 91207</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1093441934744918</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1128801747937057</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1027354435739805</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1607852124491365</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1341796267483923</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1483264533675043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>26801</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19697</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46498</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1186623899781225</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.09157661270342357</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1164936926233134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>19779; 36656</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13443; 27470</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36519; 58813</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2199089350178983</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1871299223308142</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1876140793682071</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1070202744247137</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.09666506755029569</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1021183128070132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>73317</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>59528</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>132844</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.08800393469622064</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.07457349057846345</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.0873172353217308</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>60289; 90234</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>45924; 73682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>113590; 155748</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1317150284086639</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1196495288524858</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1197244783001021</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que realizan algún voluntariado (tasa de respuesta: 99,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6725</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>5967</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>12692</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3039</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2622</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>7320</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>12909</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>11222</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>20497</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>39791</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>33864</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>73654</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>28606</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>24723</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>59319</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>50809</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>47761</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>91207</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>26801</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>19697</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>46498</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>19779</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>13443</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>36519</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>36656</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>27470</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>58813</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>73317</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>59528</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>132844</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>60289</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>45924</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>113590</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>90234</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>73682</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>155748</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>